--- a/first_catalogue.xlsx
+++ b/first_catalogue.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
   <si>
     <t xml:space="preserve">Serial Number</t>
   </si>
@@ -32,12 +32,6 @@
   </si>
   <si>
     <t xml:space="preserve">Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chess Endgames</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laszlo Polgar</t>
   </si>
   <si>
     <r>
@@ -198,11 +192,12 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="[$₹-4009]#,##0.00;[RED]\-[$₹-4009]#,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -223,12 +218,6 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FFC9211E"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -294,6 +283,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -311,10 +304,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -501,292 +490,277 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="25.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="27.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="25.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="5" t="n">
-        <f aca="false">16000-1</f>
-        <v>15999</v>
+      <c r="D2" s="6" t="n">
+        <v>599</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="6" t="n">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>599</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="B10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="6" t="n">
         <v>1199</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="4" t="s">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>1499</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="5" t="n">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="5" t="n">
+      <c r="D19" s="6" t="n">
         <v>699</v>
       </c>
     </row>

--- a/first_catalogue.xlsx
+++ b/first_catalogue.xlsx
@@ -523,7 +523,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>599</v>
+        <v>699</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -537,7 +537,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1199</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -551,7 +551,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>799</v>
+        <v>899</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -565,7 +565,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>499</v>
+        <v>599</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -593,7 +593,7 @@
         <v>14</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>199</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -607,7 +607,7 @@
         <v>16</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>499</v>
+        <v>599</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -635,7 +635,7 @@
         <v>20</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1499</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -649,7 +649,7 @@
         <v>22</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>299</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -663,7 +663,7 @@
         <v>22</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>399</v>
+        <v>499</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -677,7 +677,7 @@
         <v>22</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>499</v>
+        <v>599</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -691,7 +691,7 @@
         <v>26</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>699</v>
+        <v>799</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -705,7 +705,7 @@
         <v>28</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>499</v>
+        <v>599</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -719,7 +719,7 @@
         <v>30</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>399</v>
+        <v>499</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -733,7 +733,7 @@
         <v>32</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1299</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -747,7 +747,7 @@
         <v>32</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1199</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -761,7 +761,7 @@
         <v>35</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>699</v>
+        <v>799</v>
       </c>
     </row>
   </sheetData>

--- a/first_catalogue.xlsx
+++ b/first_catalogue.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
   <si>
     <t xml:space="preserve">Serial Number</t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t xml:space="preserve">Author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condition</t>
   </si>
   <si>
     <t xml:space="preserve">Price</t>
@@ -67,12 +70,18 @@
     <t xml:space="preserve">Goldstein</t>
   </si>
   <si>
+    <t xml:space="preserve">Almost new, unused</t>
+  </si>
+  <si>
     <t xml:space="preserve">Classical Mechanics</t>
   </si>
   <si>
     <t xml:space="preserve">Takwale &amp; Puranik</t>
   </si>
   <si>
+    <t xml:space="preserve">Used, some wear and tear</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rana &amp; Joag</t>
   </si>
   <si>
@@ -80,6 +89,9 @@
   </si>
   <si>
     <t xml:space="preserve">Sharygin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Out of print, MIR classic</t>
   </si>
   <si>
     <r>
@@ -139,16 +151,25 @@
     <t xml:space="preserve">Strogatz</t>
   </si>
   <si>
+    <t xml:space="preserve">Used, First edition, paperback</t>
+  </si>
+  <si>
     <t xml:space="preserve">Does God Play Dice</t>
   </si>
   <si>
     <t xml:space="preserve">Stewart</t>
   </si>
   <si>
+    <t xml:space="preserve">First edition, paperback</t>
+  </si>
+  <si>
     <t xml:space="preserve">Do Dice Play God</t>
   </si>
   <si>
     <t xml:space="preserve">Mathematical Treasures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Used, slightly worn</t>
   </si>
   <si>
     <t xml:space="preserve">Quantum Mechanics</t>
@@ -278,13 +299,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -295,12 +320,12 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -490,277 +515,335 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="25.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="27.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="B6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="7" t="n">
         <v>699</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="6" t="n">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="7" t="n">
         <v>1299</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="5" t="s">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>1599</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>1399</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="6" t="n">
+      <c r="E19" s="7" t="n">
         <v>799</v>
       </c>
     </row>
